--- a/working/Anjar_manning_live.xlsx
+++ b/working/Anjar_manning_live.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Anjar" sheetId="1" state="visible" r:id="rId1"/>
@@ -136,9 +136,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -176,7 +176,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -282,7 +282,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -424,7 +424,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -439,29 +439,29 @@
   <dimension ref="A1:X508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11.109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="31.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1015625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.3125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="31.7890625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="9" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="33" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="112.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="65.21875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="65.21875" customWidth="1" min="8" max="8"/>
-    <col width="32.88671875" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="22.44140625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="25.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="112.3125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="65.20703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="65.20703125" customWidth="1" min="8" max="8"/>
+    <col width="32.89453125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="22.41796875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="25.68359375" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="17" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="13.77734375" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="21.44140625" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="21.77734375" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="10.109375" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="15.88671875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="10.109375" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="13.7890625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="21.41796875" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="21.7890625" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="10.1015625" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="15.89453125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="10.1015625" bestFit="1" customWidth="1" min="18" max="18"/>
     <col width="10" bestFit="1" customWidth="1" min="19" max="20"/>
-    <col width="11.109375" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="11.1015625" bestFit="1" customWidth="1" min="21" max="21"/>
     <col width="92" bestFit="1" customWidth="1" min="22" max="22"/>
-    <col width="12.88671875" bestFit="1" customWidth="1" min="23" max="23"/>
-    <col width="23.5546875" bestFit="1" customWidth="1" min="24" max="24"/>
+    <col width="12.89453125" bestFit="1" customWidth="1" min="23" max="23"/>
+    <col width="23.5234375" bestFit="1" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37863,7 +37863,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Yarn Warehouse</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -37905,7 +37905,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Yarn Dyeing &amp; Winding</t>
         </is>
       </c>
       <c r="D480" t="n">
@@ -37947,7 +37947,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Weaving Preparatory</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Weaving Looms</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -38031,7 +38031,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Greige Folding</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -38073,7 +38073,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Fabric Processing</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -38115,7 +38115,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t xml:space="preserve">Cut &amp; Sew </t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>FG Warehouse</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -38199,7 +38199,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>TQM</t>
         </is>
       </c>
       <c r="D487" t="n">
@@ -38241,7 +38241,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -38283,7 +38283,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -38325,7 +38325,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -38367,7 +38367,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t xml:space="preserve">Pillow &amp; Poly bedding </t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D492" t="n">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>WHSL Plant</t>
+          <t xml:space="preserve">Trainees </t>
         </is>
       </c>
       <c r="D493" t="n">
@@ -38493,7 +38493,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>TT- Weaving</t>
         </is>
       </c>
       <c r="D494" t="n">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>TT- Processs</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>TT- Cut &amp; Sew</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -38619,7 +38619,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t xml:space="preserve">TT- TQM </t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t xml:space="preserve">Open end </t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -38745,7 +38745,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t xml:space="preserve">BS- Weaving </t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -38787,7 +38787,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t xml:space="preserve">BS- Process </t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>BS- Cut &amp; Sew</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -38871,7 +38871,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>BS-TQM</t>
         </is>
       </c>
       <c r="D503" t="n">
@@ -38913,7 +38913,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>New Spinning</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t xml:space="preserve">Engineering </t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -38997,7 +38997,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>TT- WGBL</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>Welspun -2</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -39081,7 +39081,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Trainees</t>
+          <t>WHSL Trainee</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -39124,28 +39124,29 @@
   <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="7.44140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="28.21875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="5.5546875" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="30" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="84.88671875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.21875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="22.6640625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="23.77734375" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="20.33203125" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="12.77734375" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="7.47265625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.3125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.20703125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="5.5234375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="30.05078125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="84.89453125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.26171875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="22.62890625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="23.7890625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="20.3671875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="12.734375" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="10" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="16.6640625" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="17" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="6.21875" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="6.21875" bestFit="1" customWidth="1" min="17" max="19"/>
+    <col width="16.62890625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="17.05078125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="6.26171875" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="11.3125" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="6.26171875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="6.20703125" bestFit="1" customWidth="1" min="18" max="19"/>
     <col width="7" bestFit="1" customWidth="1" min="20" max="20"/>
-    <col width="45" bestFit="1" customWidth="1" min="21" max="21"/>
-    <col width="11" bestFit="1" customWidth="1" min="22" max="22"/>
-    <col width="23.5546875" bestFit="1" customWidth="1" min="23" max="23"/>
-    <col width="17.88671875" bestFit="1" customWidth="1" min="24" max="24"/>
+    <col width="45.05078125" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="10.9453125" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="23.5234375" bestFit="1" customWidth="1" min="23" max="23"/>
+    <col width="17.89453125" bestFit="1" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39278,7 +39279,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -39358,7 +39359,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -39446,7 +39447,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39534,7 +39535,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -39622,7 +39623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -39710,7 +39711,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -39798,7 +39799,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -39868,7 +39869,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -39956,7 +39957,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -40031,7 +40032,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -40111,7 +40112,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -40186,7 +40187,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -40274,7 +40275,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -40354,7 +40355,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -40434,7 +40435,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -40514,7 +40515,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -40594,7 +40595,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40674,7 +40675,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40754,7 +40755,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40834,7 +40835,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40914,7 +40915,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40994,7 +40995,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -41082,7 +41083,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -41162,7 +41163,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -41242,7 +41243,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -41322,7 +41323,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -41402,7 +41403,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -41482,7 +41483,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -41562,7 +41563,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -41642,7 +41643,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -41722,7 +41723,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -41802,7 +41803,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -41882,7 +41883,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -41970,7 +41971,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -42050,7 +42051,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -42130,7 +42131,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -42210,7 +42211,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -42298,7 +42299,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -42378,7 +42379,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -42458,7 +42459,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -42538,7 +42539,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -42618,7 +42619,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -42693,7 +42694,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -42768,7 +42769,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -42843,7 +42844,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -42918,7 +42919,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -42993,7 +42994,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -43068,7 +43069,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -43143,7 +43144,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -43218,7 +43219,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -43293,7 +43294,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -44228,7 +44229,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -44313,7 +44314,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -44401,7 +44402,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -44484,7 +44485,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -44567,7 +44568,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -44655,7 +44656,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -44743,7 +44744,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -44831,7 +44832,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -44916,7 +44917,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -45001,7 +45002,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -45090,7 +45091,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -45170,7 +45171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -45250,7 +45251,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -45330,7 +45331,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -45410,7 +45411,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -45490,7 +45491,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -45570,7 +45571,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -45650,7 +45651,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -45738,7 +45739,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -45818,7 +45819,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -45898,7 +45899,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -45978,7 +45979,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -46053,7 +46054,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -46128,7 +46129,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -46203,7 +46204,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -46278,7 +46279,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -46353,7 +46354,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -46413,7 +46414,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -46473,7 +46474,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bedsheet</t>
+          <t>Spinning</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
